--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A529B749-83BC-40B0-AFA9-BD78579A7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5136BE-BB63-4EC5-98A4-E69459FF9516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="5400" windowWidth="8220" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="2190" windowWidth="20025" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -39,14 +39,14 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>r.alromi@qz.org.sa</t>
+    <t>m.albidah@qz.org.sa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +81,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Tajawal"/>
     </font>
@@ -174,8 +179,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,12 +536,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6">
-        <v>1095015416</v>
+      <c r="B2" s="5">
+        <v>1089803009</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5136BE-BB63-4EC5-98A4-E69459FF9516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A89E8B-830C-4F1E-93F3-722FDC34EEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="2190" windowWidth="20025" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="2370" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,7 +39,10 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>m.albidah@qz.org.sa</t>
+    <t>activity-leader-faleh@qz.org.sa</t>
+  </si>
+  <si>
+    <t>Takween@123456</t>
   </si>
 </sst>
 </file>
@@ -85,9 +88,10 @@
       <name val="Tajawal"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Tajawal"/>
+      <sz val="11"/>
+      <color rgb="FF424242"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -536,12 +540,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5">
-        <v>1089803009</v>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">

--- a/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
+++ b/scripts/teacher-imports/password-reset/inputs/teacher-password-updates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A89E8B-830C-4F1E-93F3-722FDC34EEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA1F90-0708-4DC0-90F5-9BF5641AD169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="2370" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تحديث كلمات المرور" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>البريد الإلكتروني</t>
   </si>
@@ -39,17 +39,14 @@
     <t>4. لا تُنشئ العملية مستخدمين جدد؛ يجب أن يكون مستخدم Firebase Auth موجودًا.</t>
   </si>
   <si>
-    <t>activity-leader-faleh@qz.org.sa</t>
-  </si>
-  <si>
-    <t>Takween@123456</t>
+    <t>n.albader@qz.org.sa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,17 +78,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tajawal"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Tajawal"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF424242"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -169,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -183,8 +169,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,15 +508,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="4" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,52 +526,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>1037656236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
